--- a/jira_export_2026-08-24.xlsx
+++ b/jira_export_2026-08-24.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>14,461 €</t>
+          <t>14,724 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>6,327 €</t>
+          <t>6,589 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>364 h</t>
+          <t>374 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -3589,7 +3589,7 @@
         <v>2</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
@@ -3602,13 +3602,13 @@
         </is>
       </c>
       <c r="N40" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="15" t="n">
         <v>787.5</v>
       </c>
-      <c r="O40" s="16" t="n">
-        <v>525</v>
-      </c>
       <c r="P40" s="15" t="n">
-        <v>420</v>
+        <v>393.75</v>
       </c>
     </row>
     <row r="41">
@@ -4525,7 +4525,7 @@
         <v>3</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>5</v>
+        <v>6.12</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>607.5</v>
       </c>
       <c r="P53" s="12" t="n">
-        <v>121.5</v>
+        <v>99.18000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4597,7 +4597,7 @@
         <v>3</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>5</v>
+        <v>6.12</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>7</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>9</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>9</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>9</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>9</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>9</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>12</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>35</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L132" s="14" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -10312,13 +10312,13 @@
       <c r="L137" s="17" t="inlineStr"/>
       <c r="M137" s="17" t="inlineStr"/>
       <c r="N137" s="18" t="n">
-        <v>67748.694</v>
+        <v>66961.194</v>
       </c>
       <c r="O137" s="18" t="n">
-        <v>14461.06</v>
+        <v>14723.56</v>
       </c>
       <c r="P137" s="18" t="n">
-        <v>74.64</v>
+        <v>73.81</v>
       </c>
     </row>
   </sheetData>
@@ -11105,26 +11105,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>141.75</v>
+        <v>146.75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>28.75</v>
+        <v>29</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>178</v>
+        <v>183.75</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>64.25</v>
+        <v>66.25</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>601.65</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>98.5</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -11251,16 +11251,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>378092</v>
+        <v>382650</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>142794</v>
+        <v>147615</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>235298</v>
+        <v>235035</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>148528</v>
+        <v>148266</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -11276,16 +11276,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>169020</v>
+        <v>170493</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>64105</v>
+        <v>65841</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>104915</v>
+        <v>104652</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>87499</v>
+        <v>87237</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>11307</v>
@@ -11301,10 +11301,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>209072</v>
+        <v>212157</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>78689</v>
+        <v>81774</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>130383</v>
@@ -11330,7 +11330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11354,7 +11354,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 13 commande(s)</t>
+          <t>Épics créées ce mois — 14 commande(s)</t>
         </is>
       </c>
     </row>
@@ -11409,22 +11409,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35171</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35165</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LORGUES</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00178865</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -11454,12 +11454,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35156</t>
+          <t>PDMDEP-35171</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35148</t>
+          <t>PDMDEP-35165</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Les Portes En Ré</t>
+          <t>MAIRIE DE LORGUES</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -11489,32 +11489,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00178841</t>
+          <t>00178865</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35139</t>
+          <t>PDMDEP-35156</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35148</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>Mairie de Les Portes En Ré</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -11534,22 +11534,22 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00178821</t>
+          <t>00178841</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -11579,22 +11579,22 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>985</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35088</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35082</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>FREJUS</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -11624,32 +11624,32 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00152501</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>3541.5</v>
+        <v>985</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35008</t>
+          <t>PDMDEP-35088</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35000</t>
+          <t>PDMDEP-35082</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
+          <t>FREJUS</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -11669,32 +11669,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00178436</t>
+          <t>00152501</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>500</v>
+        <v>3541.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-35008</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -11714,37 +11714,37 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178436</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>4050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35188</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35184</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -11759,32 +11759,32 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00178947</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35041</t>
+          <t>PDMDEP-35188</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -11804,32 +11804,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00178778</t>
+          <t>00178947</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>0</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34993</t>
+          <t>PDMDEP-35041</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34989</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00178306</t>
+          <t>00178778</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -11894,22 +11894,22 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34970</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34966</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -11939,83 +11939,107 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00146508</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-34970</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34966</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Commune de Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>00146508</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I17" s="25" t="n">
+      <c r="I18" s="26" t="n">
         <v>2300</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>13 commande(s)</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>15076</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B19" s="17" t="n"/>
@@ -12026,17 +12050,17 @@
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>6 commande(s)</t>
+          <t>14 commande(s)</t>
         </is>
       </c>
       <c r="I19" s="24" t="n">
-        <v>6000</v>
+        <v>19898</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B20" s="17" t="n"/>
@@ -12047,11 +12071,32 @@
       <c r="G20" s="17" t="n"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>7 commande(s)</t>
+          <t>6 commande(s)</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>9076</v>
+        <v>7736</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>8 commande(s)</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="n">
+        <v>12162</v>
       </c>
     </row>
   </sheetData>
@@ -12065,12 +12110,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -12086,7 +12131,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>4 clôture(s) : 4 projet(s), 0 rework</t>
+          <t>5 clôture(s) : 5 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -12216,59 +12261,89 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-30044</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-34848</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des a</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>COMMUNE DE BRUAY LA BUISSIERE</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F9" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n">
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-08-24.xlsx
+++ b/jira_export_2026-08-24.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>14,724 €</t>
+          <t>16,407 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>8,134 €</t>
+          <t>9,818 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>374 h</t>
+          <t>376 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P137"/>
+  <dimension ref="A1:P139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2093,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="P20" s="15" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="21">
@@ -2550,12 +2550,12 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration Placier + ODP</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2601,19 +2601,19 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O26" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O26" s="15" t="n">
+        <v>726.25</v>
       </c>
       <c r="P26" s="15" t="n">
         <v>0</v>
@@ -2622,32 +2622,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2657,69 +2657,69 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O27" s="16" t="n">
-        <v>1080</v>
+        <v>0</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>70.81999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2729,49 +2729,49 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O28" s="16" t="n">
-        <v>367.5</v>
+        <v>1080</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>0</v>
+        <v>70.81999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -2817,19 +2817,19 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O29" s="16" t="n">
-        <v>0</v>
+        <v>367.5</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
@@ -2838,42 +2838,42 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
@@ -2885,14 +2885,22 @@
         <v>2</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L30" s="14" t="inlineStr"/>
-      <c r="M30" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34201</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>00171162</t>
+        </is>
+      </c>
       <c r="N30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="15" t="n">
+        <v>1662</v>
+      </c>
+      <c r="O30" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="15" t="n">
@@ -2902,69 +2910,61 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34227</t>
-        </is>
-      </c>
-      <c r="M31" s="11" t="inlineStr">
-        <is>
-          <t>2026-0210095</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L31" s="11" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr"/>
       <c r="N31" s="12" t="n">
-        <v>9623.1</v>
-      </c>
-      <c r="O31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="12" t="n">
@@ -2974,12 +2974,12 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
@@ -3025,16 +3025,16 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3046,12 +3046,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3081,32 +3081,32 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3118,27 +3118,27 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34000</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Imprimante Bixolon</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -3158,36 +3158,44 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L34" s="14" t="inlineStr"/>
-      <c r="M34" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34070</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="inlineStr">
+        <is>
+          <t>00170468</t>
+        </is>
+      </c>
       <c r="N34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="15" t="n">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>90</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34000</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3197,12 +3205,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Imprimante Bixolon</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3212,12 +3220,12 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -3229,22 +3237,14 @@
         <v>2</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L35" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33991</t>
-        </is>
-      </c>
-      <c r="M35" s="11" t="inlineStr">
-        <is>
-          <t>00170408</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L35" s="11" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr"/>
       <c r="N35" s="12" t="n">
-        <v>510</v>
-      </c>
-      <c r="O35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="12" t="n">
@@ -3254,32 +3254,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3289,64 +3289,64 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>9.75</v>
+        <v>0.25</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="O36" s="15" t="n">
-        <v>1118.61</v>
+        <v>510</v>
+      </c>
+      <c r="O36" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>114.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3373,57 +3373,57 @@
         <v>2</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>220</v>
-      </c>
-      <c r="O37" s="16" t="n">
-        <v>0</v>
+        <v>242.9</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <v>1118.61</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>0</v>
+        <v>114.73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3433,34 +3433,34 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="O38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3470,27 +3470,27 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3517,22 +3517,22 @@
         <v>2</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>680</v>
-      </c>
-      <c r="O39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
@@ -3542,32 +3542,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3577,49 +3577,49 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="15" t="n">
-        <v>787.5</v>
+        <v>680</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
-        <v>393.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3661,37 +3661,37 @@
         <v>2</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>416.29</v>
+        <v>787.5</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>46.25</v>
+        <v>393.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3733,52 +3733,52 @@
         <v>2</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O42" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O42" s="15" t="n">
+        <v>416.29</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>0</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3798,27 +3798,27 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3830,32 +3830,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33638</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOULINS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier et MEP module Caisse</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3865,34 +3865,34 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33647</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00169251</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>4424</v>
-      </c>
-      <c r="O44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="15" t="n">
@@ -3902,32 +3902,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3937,64 +3937,64 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>4040</v>
+        <v>920</v>
       </c>
       <c r="O45" s="16" t="n">
-        <v>3535</v>
+        <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>1571.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
@@ -4025,16 +4025,16 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33647</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169251</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>1017.5</v>
+        <v>4424</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4046,27 +4046,27 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4081,69 +4081,69 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1416</v>
+        <v>4040</v>
       </c>
       <c r="O47" s="16" t="n">
-        <v>0</v>
+        <v>3535</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>0</v>
+        <v>1571.11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4158,59 +4158,59 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>171.4</v>
+        <v>1017.5</v>
       </c>
       <c r="O48" s="16" t="n">
-        <v>0</v>
+        <v>691.9</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>0</v>
+        <v>691.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4241,16 +4241,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>344</v>
+        <v>1416</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4262,12 +4262,12 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4277,12 +4277,12 @@
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4302,59 +4302,59 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>514.2</v>
-      </c>
-      <c r="O50" s="15" t="n">
-        <v>642.75</v>
+        <v>171.4</v>
+      </c>
+      <c r="O50" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>514.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
@@ -4385,16 +4385,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4406,32 +4406,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4441,69 +4441,69 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>149</v>
-      </c>
-      <c r="O52" s="16" t="n">
-        <v>0</v>
+        <v>514.2</v>
+      </c>
+      <c r="O52" s="15" t="n">
+        <v>642.75</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>0</v>
+        <v>514.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4518,64 +4518,64 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="O53" s="16" t="n">
-        <v>607.5</v>
+        <v>0</v>
       </c>
       <c r="P53" s="12" t="n">
-        <v>99.18000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4585,34 +4585,34 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="15" t="n">
+        <v>149</v>
+      </c>
+      <c r="O54" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
@@ -4622,32 +4622,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4657,69 +4657,69 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>5</v>
+        <v>6.12</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>910</v>
-      </c>
-      <c r="O55" s="12" t="n">
-        <v>910</v>
+        <v>625</v>
+      </c>
+      <c r="O55" s="16" t="n">
+        <v>607.5</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>182</v>
+        <v>99.18000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4729,34 +4729,34 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="15" t="n">
@@ -4766,27 +4766,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4806,64 +4806,64 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0.25</v>
+        <v>5</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>323.7</v>
+        <v>910</v>
       </c>
       <c r="P57" s="12" t="n">
-        <v>1294.8</v>
+        <v>182</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
@@ -4889,16 +4889,16 @@
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4910,27 +4910,27 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4950,59 +4950,59 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>400</v>
-      </c>
-      <c r="O59" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O59" s="12" t="n">
+        <v>323.7</v>
       </c>
       <c r="P59" s="12" t="n">
-        <v>0</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5022,29 +5022,29 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="O60" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
@@ -5054,32 +5054,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5089,49 +5089,49 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>2.75</v>
+        <v>1</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>1294.224</v>
+        <v>400</v>
       </c>
       <c r="O61" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>79.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H62" s="14" t="inlineStr">
@@ -5166,17 +5166,25 @@
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L62" s="14" t="inlineStr"/>
-      <c r="M62" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L62" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32772</t>
+        </is>
+      </c>
+      <c r="M62" s="14" t="inlineStr">
+        <is>
+          <t>00163806</t>
+        </is>
+      </c>
       <c r="N62" s="15" t="n">
         <v>0</v>
       </c>
@@ -5190,12 +5198,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5205,12 +5213,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5230,101 +5238,93 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>142.1</v>
+        <v>1294.224</v>
       </c>
       <c r="O63" s="16" t="n">
-        <v>0</v>
+        <v>219.36</v>
       </c>
       <c r="P63" s="12" t="n">
-        <v>0</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-32470</t>
-        </is>
-      </c>
-      <c r="M64" s="14" t="inlineStr">
-        <is>
-          <t>00161950</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L64" s="14" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
       <c r="N64" s="15" t="n">
-        <v>2335</v>
-      </c>
-      <c r="O64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5334,27 +5334,27 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5374,29 +5374,29 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="12" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="O65" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -5406,27 +5406,27 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5457,16 +5457,16 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5478,12 +5478,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5518,29 +5518,29 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>910</v>
-      </c>
-      <c r="O67" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
@@ -5550,23 +5550,27 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr"/>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5586,7 +5590,7 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
@@ -5597,16 +5601,16 @@
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>255</v>
+        <v>450</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5618,32 +5622,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5653,64 +5657,60 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="n">
-        <v>100</v>
+        <v>910</v>
+      </c>
+      <c r="O69" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr"/>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
@@ -5741,16 +5741,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>590.15</v>
+        <v>255</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5762,27 +5762,27 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5802,64 +5802,64 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O71" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
+        <v>100</v>
       </c>
       <c r="P71" s="12" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5874,29 +5874,29 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
+        <v>590.15</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5906,12 +5906,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -5957,16 +5957,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>285</v>
+        <v>1000</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5978,12 +5978,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6013,34 +6013,34 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>1325</v>
-      </c>
-      <c r="O74" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
@@ -6050,32 +6050,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6101,16 +6101,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6122,32 +6122,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
@@ -6173,16 +6173,16 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>588</v>
+        <v>1325</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6194,32 +6194,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6229,32 +6229,32 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K77" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>203.5</v>
+        <v>120</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6266,27 +6266,27 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6306,27 +6306,27 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K78" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>300</v>
+        <v>588</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6338,32 +6338,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6373,98 +6373,106 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>700</v>
-      </c>
-      <c r="O79" s="12" t="n">
-        <v>967.05</v>
+        <v>203.5</v>
+      </c>
+      <c r="O79" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
-        <v>78.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L80" s="14" t="inlineStr"/>
-      <c r="M80" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L80" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31596</t>
+        </is>
+      </c>
+      <c r="M80" s="14" t="inlineStr">
+        <is>
+          <t>00157967</t>
+        </is>
+      </c>
       <c r="N80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="O80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6474,27 +6482,27 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6514,101 +6522,93 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>6</v>
+        <v>12.25</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O81" s="16" t="n">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="O81" s="12" t="n">
+        <v>967.05</v>
       </c>
       <c r="P81" s="12" t="n">
-        <v>0</v>
+        <v>78.94</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31360</t>
-        </is>
-      </c>
-      <c r="M82" s="14" t="inlineStr">
-        <is>
-          <t>00157041</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L82" s="14" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
       <c r="N82" s="15" t="n">
-        <v>210</v>
-      </c>
-      <c r="O82" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6618,32 +6618,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6653,32 +6653,32 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>281</v>
+        <v>416.475</v>
       </c>
       <c r="O83" s="16" t="n">
         <v>0</v>
@@ -6690,12 +6690,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
@@ -6741,16 +6741,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6762,12 +6762,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
@@ -6813,16 +6813,16 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="O85" s="16" t="n">
         <v>0</v>
@@ -6834,12 +6834,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="O86" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
@@ -6906,12 +6906,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -6946,27 +6946,27 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K87" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O87" s="16" t="n">
         <v>0</v>
@@ -6978,32 +6978,32 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -7013,34 +7013,34 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>8.75</v>
+        <v>1.5</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>690</v>
-      </c>
-      <c r="O88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7050,69 +7050,69 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="O89" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7122,27 +7122,27 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -7162,29 +7162,29 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>2.42</v>
+        <v>8.75</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="15" t="n">
+        <v>690</v>
+      </c>
+      <c r="O90" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7194,12 +7194,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -7234,29 +7234,29 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>2.42</v>
+        <v>1</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O91" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7317,18 +7317,18 @@
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7338,32 +7338,32 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -7373,32 +7373,32 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>725</v>
+        <v>187.5</v>
       </c>
       <c r="O93" s="16" t="n">
         <v>0</v>
@@ -7410,26 +7410,28 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -7443,34 +7445,34 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="15" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -7480,32 +7482,32 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
@@ -7515,34 +7517,34 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="O95" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7552,12 +7554,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7567,13 +7569,11 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E96" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v/>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -7592,23 +7592,23 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7675,12 +7675,12 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
@@ -7819,18 +7819,18 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O99" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7840,12 +7840,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7855,11 +7855,13 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E100" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -7873,28 +7875,28 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>1.25</v>
+        <v>0.85</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7910,12 +7912,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7925,11 +7927,13 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E101" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
@@ -7948,29 +7952,29 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>8.25</v>
+        <v>0.85</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O101" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -7980,12 +7984,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -7995,7 +7999,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -8013,34 +8017,34 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8050,28 +8054,26 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v/>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
@@ -8090,23 +8092,23 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.25</v>
+        <v>8.25</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8122,12 +8124,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8137,13 +8139,11 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E104" s="14" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="n">
+        <v/>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -8152,31 +8152,39 @@
       </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="14" t="inlineStr"/>
-      <c r="M104" s="14" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L104" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="M104" s="14" t="inlineStr">
+        <is>
+          <t>00141205</t>
+        </is>
+      </c>
       <c r="N104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8186,12 +8194,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8201,11 +8209,13 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
@@ -8224,23 +8234,23 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
@@ -8256,26 +8266,28 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E106" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
@@ -8284,35 +8296,27 @@
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L106" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27995</t>
-        </is>
-      </c>
-      <c r="M106" s="14" t="inlineStr">
-        <is>
-          <t>501218</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L106" s="14" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
       <c r="N106" s="15" t="n">
         <v>0</v>
       </c>
@@ -8326,22 +8330,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8364,23 +8368,23 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
@@ -8396,22 +8400,22 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8434,23 +8438,23 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
@@ -8466,12 +8470,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8481,7 +8485,7 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8504,23 +8508,23 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1.31</v>
+        <v>3</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
@@ -8536,12 +8540,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8551,7 +8555,7 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8574,23 +8578,23 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
         <v>13</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
@@ -8621,7 +8625,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8655,12 +8659,12 @@
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8725,12 +8729,12 @@
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
@@ -8746,22 +8750,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8779,34 +8783,34 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O113" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8816,12 +8820,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8831,7 +8835,7 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8847,20 +8851,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H114" s="14" t="inlineStr"/>
+      <c r="H114" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L114" s="14" t="inlineStr"/>
-      <c r="M114" s="14" t="inlineStr"/>
+        <v>1.31</v>
+      </c>
+      <c r="L114" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M114" s="14" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
       <c r="N114" s="15" t="n">
         <v>0</v>
       </c>
@@ -8874,12 +8890,12 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8889,7 +8905,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8907,34 +8923,34 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O115" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8944,12 +8960,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -8959,7 +8975,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -8975,14 +8991,10 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H116" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H116" s="14" t="inlineStr"/>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
@@ -8991,16 +9003,8 @@
       <c r="K116" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L116" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28035</t>
-        </is>
-      </c>
-      <c r="M116" s="14" t="inlineStr">
-        <is>
-          <t>468660</t>
-        </is>
-      </c>
+      <c r="L116" s="14" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
       <c r="N116" s="15" t="n">
         <v>0</v>
       </c>
@@ -9014,12 +9018,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9029,7 +9033,7 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9047,34 +9051,34 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O117" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9084,12 +9088,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9099,7 +9103,7 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9112,23 +9116,35 @@
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H118" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L118" s="14" t="inlineStr"/>
-      <c r="M118" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L118" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M118" s="14" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N118" s="15" t="n">
         <v>0</v>
       </c>
@@ -9142,12 +9158,12 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -9157,7 +9173,7 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9175,34 +9191,34 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O119" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="12" t="n">
@@ -9212,22 +9228,22 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9240,35 +9256,23 @@
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H120" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="inlineStr"/>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L120" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27568</t>
-        </is>
-      </c>
-      <c r="M120" s="14" t="inlineStr">
-        <is>
-          <t>471958</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L120" s="14" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
       <c r="N120" s="15" t="n">
         <v>0</v>
       </c>
@@ -9282,12 +9286,12 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9297,7 +9301,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9310,7 +9314,7 @@
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
@@ -9320,17 +9324,25 @@
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L121" s="11" t="inlineStr"/>
-      <c r="M121" s="11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N121" s="12" t="n">
         <v>0</v>
       </c>
@@ -9344,12 +9356,12 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
@@ -9359,7 +9371,7 @@
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9372,27 +9384,35 @@
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L122" s="14" t="inlineStr"/>
-      <c r="M122" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L122" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M122" s="14" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N122" s="15" t="n">
         <v>0</v>
       </c>
@@ -9406,22 +9426,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9429,44 +9449,36 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M123" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr"/>
+      <c r="M123" s="11" t="inlineStr"/>
       <c r="N123" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O123" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="12" t="n">
@@ -9476,12 +9488,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
@@ -9491,7 +9503,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9504,39 +9516,31 @@
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M124" s="14" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L124" s="14" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
       <c r="N124" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O124" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="15" t="n">
@@ -9546,22 +9550,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9569,36 +9573,44 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L125" s="11" t="inlineStr"/>
-      <c r="M125" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N125" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O125" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="12" t="n">
@@ -9608,12 +9620,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9623,7 +9635,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9636,7 +9648,7 @@
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H126" s="14" t="inlineStr">
@@ -9646,29 +9658,29 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O126" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="15" t="n">
@@ -9678,12 +9690,12 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -9693,7 +9705,7 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9716,14 +9728,14 @@
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L127" s="11" t="inlineStr"/>
       <c r="M127" s="11" t="inlineStr"/>
@@ -9740,12 +9752,12 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
@@ -9755,7 +9767,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9778,17 +9790,25 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L128" s="14" t="inlineStr"/>
-      <c r="M128" s="14" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L128" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M128" s="14" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N128" s="15" t="n">
         <v>0</v>
       </c>
@@ -9802,22 +9822,22 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9830,7 +9850,7 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
@@ -9840,25 +9860,17 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L129" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M129" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L129" s="11" t="inlineStr"/>
+      <c r="M129" s="11" t="inlineStr"/>
       <c r="N129" s="12" t="n">
         <v>0</v>
       </c>
@@ -9872,22 +9884,22 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -9905,30 +9917,22 @@
       </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L130" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M130" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L130" s="14" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
       <c r="N130" s="15" t="n">
         <v>0</v>
       </c>
@@ -9942,22 +9946,22 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -9970,27 +9974,35 @@
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L131" s="11" t="inlineStr"/>
-      <c r="M131" s="11" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L131" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M131" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N131" s="12" t="n">
         <v>0</v>
       </c>
@@ -10004,28 +10016,26 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E132" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="n">
+        <v/>
       </c>
       <c r="F132" s="14" t="inlineStr">
         <is>
@@ -10039,22 +10049,30 @@
       </c>
       <c r="H132" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L132" s="14" t="inlineStr"/>
-      <c r="M132" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L132" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M132" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N132" s="15" t="n">
         <v>0</v>
       </c>
@@ -10068,24 +10086,26 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C133" s="11" t="inlineStr"/>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E133" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="n">
+        <v/>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
@@ -10104,14 +10124,14 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="L133" s="11" t="inlineStr"/>
       <c r="M133" s="11" t="inlineStr"/>
@@ -10128,27 +10148,27 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+          <t>[CD 14] Paramétrages</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F134" s="14" t="inlineStr">
@@ -10168,14 +10188,14 @@
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="L134" s="14" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -10192,21 +10212,25 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr"/>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10214,20 +10238,24 @@
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H135" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="L135" s="11" t="inlineStr"/>
       <c r="M135" s="11" t="inlineStr"/>
@@ -10244,21 +10272,29 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
-        </is>
-      </c>
-      <c r="C136" s="14" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C136" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
-        </is>
-      </c>
-      <c r="E136" s="14" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F136" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10266,20 +10302,24 @@
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H136" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L136" s="14" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -10294,31 +10334,135 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="17" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1326</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr"/>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr"/>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr"/>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="J137" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr"/>
+      <c r="M137" s="11" t="inlineStr"/>
+      <c r="N137" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1320</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="C138" s="14" t="inlineStr"/>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="inlineStr"/>
+      <c r="F138" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G138" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H138" s="14" t="inlineStr"/>
+      <c r="I138" s="14" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="J138" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L138" s="14" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+      <c r="N138" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B137" s="17" t="inlineStr"/>
-      <c r="C137" s="17" t="inlineStr"/>
-      <c r="D137" s="17" t="inlineStr"/>
-      <c r="E137" s="17" t="inlineStr"/>
-      <c r="F137" s="17" t="inlineStr"/>
-      <c r="G137" s="17" t="inlineStr"/>
-      <c r="H137" s="17" t="inlineStr"/>
-      <c r="I137" s="17" t="inlineStr"/>
-      <c r="J137" s="17" t="inlineStr"/>
-      <c r="K137" s="17" t="inlineStr"/>
-      <c r="L137" s="17" t="inlineStr"/>
-      <c r="M137" s="17" t="inlineStr"/>
-      <c r="N137" s="18" t="n">
+      <c r="B139" s="17" t="inlineStr"/>
+      <c r="C139" s="17" t="inlineStr"/>
+      <c r="D139" s="17" t="inlineStr"/>
+      <c r="E139" s="17" t="inlineStr"/>
+      <c r="F139" s="17" t="inlineStr"/>
+      <c r="G139" s="17" t="inlineStr"/>
+      <c r="H139" s="17" t="inlineStr"/>
+      <c r="I139" s="17" t="inlineStr"/>
+      <c r="J139" s="17" t="inlineStr"/>
+      <c r="K139" s="17" t="inlineStr"/>
+      <c r="L139" s="17" t="inlineStr"/>
+      <c r="M139" s="17" t="inlineStr"/>
+      <c r="N139" s="18" t="n">
         <v>66961.194</v>
       </c>
-      <c r="O137" s="18" t="n">
-        <v>14723.56</v>
-      </c>
-      <c r="P137" s="18" t="n">
-        <v>73.81</v>
+      <c r="O139" s="18" t="n">
+        <v>16406.71</v>
+      </c>
+      <c r="P139" s="18" t="n">
+        <v>81.53</v>
       </c>
     </row>
   </sheetData>
@@ -10456,6 +10600,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11105,7 +11251,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>146.75</v>
+        <v>148.5</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>29</v>
@@ -11114,7 +11260,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>183.75</v>
+        <v>185.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>66.25</v>
@@ -11124,7 +11270,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -11251,10 +11397,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>382650</v>
+        <v>380967</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>147615</v>
+        <v>145932</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>235035</v>
@@ -11301,10 +11447,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>212157</v>
+        <v>210474</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>81774</v>
+        <v>80091</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>130383</v>

--- a/jira_export_2026-08-24.xlsx
+++ b/jira_export_2026-08-24.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>376 h</t>
+          <t>385 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P139"/>
+  <dimension ref="A1:P142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1525,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
@@ -2262,27 +2262,27 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA FLÈCHE] - Migration GEODP Placier et ODP</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2302,29 +2302,29 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>895</v>
-      </c>
-      <c r="O22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="15" t="n">
@@ -2334,12 +2334,12 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2369,35 +2369,35 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
@@ -2406,12 +2406,12 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Achat nouveau PAX A920</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
@@ -2457,19 +2457,19 @@
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34345</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00171711</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="15" t="n">
-        <v>50</v>
+        <v>769.5</v>
+      </c>
+      <c r="O24" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P24" s="15" t="n">
         <v>0</v>
@@ -2478,27 +2478,27 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration Placier + ODP</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2529,19 +2529,19 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O25" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O25" s="12" t="n">
+        <v>726.25</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
@@ -2550,12 +2550,12 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Migration Placier + ODP</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2601,19 +2601,19 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="15" t="n">
-        <v>726.25</v>
+        <v>2127.2</v>
+      </c>
+      <c r="O26" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P26" s="15" t="n">
         <v>0</v>
@@ -2622,32 +2622,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2657,69 +2657,69 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2127.2</v>
+        <v>4536</v>
       </c>
       <c r="O27" s="16" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>0</v>
+        <v>70.81999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2729,49 +2729,49 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>4536</v>
+        <v>525</v>
       </c>
       <c r="O28" s="16" t="n">
-        <v>1080</v>
+        <v>367.5</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>70.81999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -2817,19 +2817,19 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>525</v>
+        <v>1662</v>
       </c>
       <c r="O29" s="16" t="n">
-        <v>367.5</v>
+        <v>0</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
@@ -2838,42 +2838,42 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
@@ -2885,22 +2885,14 @@
         <v>2</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34201</t>
-        </is>
-      </c>
-      <c r="M30" s="14" t="inlineStr">
-        <is>
-          <t>00171162</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L30" s="14" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
       <c r="N30" s="15" t="n">
-        <v>1662</v>
-      </c>
-      <c r="O30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="15" t="n">
@@ -2910,61 +2902,69 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L31" s="11" t="inlineStr"/>
-      <c r="M31" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34227</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>2026-0210095</t>
+        </is>
+      </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="12" t="n">
+        <v>9623.1</v>
+      </c>
+      <c r="O31" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="12" t="n">
@@ -2974,12 +2974,12 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
@@ -3025,16 +3025,16 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>9623.1</v>
+        <v>707</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3046,12 +3046,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3081,64 +3081,64 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>707</v>
+        <v>300</v>
       </c>
       <c r="O33" s="16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P33" s="12" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34000</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Imprimante Bixolon</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -3158,44 +3158,36 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L34" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34070</t>
-        </is>
-      </c>
-      <c r="M34" s="14" t="inlineStr">
-        <is>
-          <t>00170468</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L34" s="14" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
       <c r="N34" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="O34" s="16" t="n">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="O34" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34000</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3205,12 +3197,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Imprimante Bixolon</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3220,12 +3212,12 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -3237,14 +3229,22 @@
         <v>2</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L35" s="11" t="inlineStr"/>
-      <c r="M35" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33991</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>00170408</t>
+        </is>
+      </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="12" t="n">
+        <v>510</v>
+      </c>
+      <c r="O35" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="12" t="n">
@@ -3254,32 +3254,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3289,64 +3289,64 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0.25</v>
+        <v>9.75</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>510</v>
-      </c>
-      <c r="O36" s="16" t="n">
-        <v>0</v>
+        <v>242.9</v>
+      </c>
+      <c r="O36" s="15" t="n">
+        <v>1118.61</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>0</v>
+        <v>114.73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3373,57 +3373,57 @@
         <v>2</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="O37" s="12" t="n">
-        <v>1118.61</v>
+        <v>220</v>
+      </c>
+      <c r="O37" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>114.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3433,34 +3433,34 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>220</v>
-      </c>
-      <c r="O38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3470,27 +3470,27 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3517,22 +3517,22 @@
         <v>2</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="12" t="n">
+        <v>680</v>
+      </c>
+      <c r="O39" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
@@ -3542,32 +3542,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3577,49 +3577,49 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>680</v>
-      </c>
-      <c r="O40" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O40" s="15" t="n">
+        <v>787.5</v>
       </c>
       <c r="P40" s="15" t="n">
-        <v>0</v>
+        <v>393.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3661,37 +3661,37 @@
         <v>2</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>787.5</v>
+        <v>416.29</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>393.75</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3733,52 +3733,52 @@
         <v>2</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="15" t="n">
-        <v>416.29</v>
+        <v>1890</v>
+      </c>
+      <c r="O42" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>46.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3798,29 +3798,29 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="12" t="n">
@@ -3830,12 +3830,12 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="15" t="n">
+        <v>920</v>
+      </c>
+      <c r="O44" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="15" t="n">
@@ -3902,32 +3902,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3937,32 +3937,32 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33647</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169251</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>920</v>
+        <v>4424</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3974,12 +3974,12 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33638</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOULINS</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier et MEP module Caisse</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4014,59 +4014,59 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33647</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00169251</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>4424</v>
+        <v>4040</v>
       </c>
       <c r="O46" s="16" t="n">
-        <v>0</v>
+        <v>3535</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>0</v>
+        <v>1571.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -4093,52 +4093,52 @@
         <v>2</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>4040</v>
+        <v>1017.5</v>
       </c>
       <c r="O47" s="16" t="n">
-        <v>3535</v>
+        <v>691.9</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>1571.11</v>
+        <v>691.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4153,69 +4153,69 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>1017.5</v>
+        <v>1416</v>
       </c>
       <c r="O48" s="16" t="n">
-        <v>691.9</v>
+        <v>0</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>691.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4241,16 +4241,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1416</v>
+        <v>171.4</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4262,32 +4262,32 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4313,16 +4313,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>171.4</v>
+        <v>344</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4334,32 +4334,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4381,57 +4381,57 @@
         <v>3</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>344</v>
-      </c>
-      <c r="O51" s="16" t="n">
-        <v>0</v>
+        <v>514.2</v>
+      </c>
+      <c r="O51" s="12" t="n">
+        <v>642.75</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>0</v>
+        <v>514.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4446,59 +4446,59 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>514.2</v>
-      </c>
-      <c r="O52" s="15" t="n">
-        <v>642.75</v>
+        <v>500</v>
+      </c>
+      <c r="O52" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>514.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4529,16 +4529,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>500</v>
+        <v>149</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4550,32 +4550,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4585,38 +4585,38 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>149</v>
+        <v>625</v>
       </c>
       <c r="O54" s="16" t="n">
-        <v>0</v>
+        <v>607.5</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>0</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="55">
@@ -4669,57 +4669,57 @@
         <v>3</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>6.12</v>
+        <v>7.38</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>625</v>
-      </c>
-      <c r="O55" s="16" t="n">
-        <v>607.5</v>
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>99.18000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4729,49 +4729,49 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>6.12</v>
+        <v>5</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="P56" s="15" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4806,59 +4806,59 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>910</v>
-      </c>
-      <c r="O57" s="12" t="n">
-        <v>910</v>
+        <v>1207</v>
+      </c>
+      <c r="O57" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4878,64 +4878,64 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O58" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O58" s="15" t="n">
+        <v>323.7</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>0</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4945,69 +4945,69 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="12" t="n">
-        <v>323.7</v>
+        <v>500</v>
+      </c>
+      <c r="O59" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
-        <v>1294.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
@@ -5029,20 +5029,20 @@
         <v>4</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5054,32 +5054,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5089,34 +5089,34 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>400</v>
-      </c>
-      <c r="O61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5126,12 +5126,12 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5166,44 +5166,44 @@
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0.25</v>
+        <v>2.75</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="15" t="n">
-        <v>0</v>
+        <v>1294.224</v>
+      </c>
+      <c r="O62" s="16" t="n">
+        <v>219.36</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>0</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
@@ -5238,44 +5238,36 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L63" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32629</t>
-        </is>
-      </c>
-      <c r="M63" s="11" t="inlineStr">
-        <is>
-          <t>00163182</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L63" s="11" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr"/>
       <c r="N63" s="12" t="n">
-        <v>1294.224</v>
-      </c>
-      <c r="O63" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
-        <v>79.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5285,12 +5277,12 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5300,7 +5292,7 @@
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H64" s="14" t="inlineStr">
@@ -5317,14 +5309,22 @@
         <v>4</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L64" s="14" t="inlineStr"/>
-      <c r="M64" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L64" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32556</t>
+        </is>
+      </c>
+      <c r="M64" s="14" t="inlineStr">
+        <is>
+          <t>00162313</t>
+        </is>
+      </c>
       <c r="N64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="15" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="O64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5334,32 +5334,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5369,32 +5369,32 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>142.1</v>
+        <v>2335</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5406,32 +5406,32 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5441,34 +5441,34 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>2335</v>
-      </c>
-      <c r="O66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
@@ -5478,32 +5478,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5513,34 +5513,34 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="O67" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
@@ -5550,32 +5550,32 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>450</v>
+        <v>910</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5622,32 +5622,28 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr"/>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5657,32 +5653,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>910</v>
+        <v>255</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5694,23 +5690,27 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr"/>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5737,52 +5737,52 @@
         <v>5</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>255</v>
-      </c>
-      <c r="O70" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O70" s="15" t="n">
+        <v>100</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5797,49 +5797,49 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
-        <v>100</v>
+        <v>590.15</v>
+      </c>
+      <c r="O71" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
@@ -5885,16 +5885,16 @@
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>590.15</v>
+        <v>1000</v>
       </c>
       <c r="O72" s="16" t="n">
         <v>0</v>
@@ -5906,32 +5906,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5941,34 +5941,34 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O73" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -5978,32 +5978,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6013,34 +6013,34 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
@@ -6050,32 +6050,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6101,16 +6101,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>285</v>
+        <v>1325</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6122,12 +6122,12 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
@@ -6173,16 +6173,16 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>1325</v>
+        <v>120</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6194,32 +6194,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -6245,16 +6245,16 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>120</v>
+        <v>588</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6266,27 +6266,27 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6301,32 +6301,32 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K78" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>588</v>
+        <v>203.5</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6338,12 +6338,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
@@ -6389,16 +6389,16 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>203.5</v>
+        <v>300</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6410,32 +6410,32 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6445,49 +6445,49 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="O80" s="16" t="n">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="O80" s="15" t="n">
+        <v>967.05</v>
       </c>
       <c r="P80" s="15" t="n">
-        <v>0</v>
+        <v>78.94</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
@@ -6529,52 +6529,44 @@
         <v>6</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="L81" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31546</t>
-        </is>
-      </c>
-      <c r="M81" s="11" t="inlineStr">
-        <is>
-          <t>00157816</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L81" s="11" t="inlineStr"/>
+      <c r="M81" s="11" t="inlineStr"/>
       <c r="N81" s="12" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="O81" s="12" t="n">
-        <v>967.05</v>
+        <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
-        <v>78.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
@@ -6584,7 +6576,7 @@
       </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H82" s="14" t="inlineStr">
@@ -6594,21 +6586,29 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L82" s="14" t="inlineStr"/>
-      <c r="M82" s="14" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="L82" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31468</t>
+        </is>
+      </c>
+      <c r="M82" s="14" t="inlineStr">
+        <is>
+          <t>00157346</t>
+        </is>
+      </c>
       <c r="N82" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="15" t="n">
+        <v>416.475</v>
+      </c>
+      <c r="O82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6618,32 +6618,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6653,32 +6653,32 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>416.475</v>
+        <v>210</v>
       </c>
       <c r="O83" s="16" t="n">
         <v>0</v>
@@ -6690,12 +6690,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -6741,16 +6741,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6762,12 +6762,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
@@ -6813,16 +6813,16 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>281</v>
+        <v>130</v>
       </c>
       <c r="O85" s="16" t="n">
         <v>0</v>
@@ -6834,12 +6834,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
@@ -6885,16 +6885,16 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O86" s="16" t="n">
         <v>0</v>
@@ -6906,12 +6906,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -6946,29 +6946,29 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>255</v>
-      </c>
-      <c r="O87" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -6978,12 +6978,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
@@ -7018,29 +7018,29 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="O88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7050,32 +7050,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7085,32 +7085,32 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>140</v>
+        <v>690</v>
       </c>
       <c r="O89" s="16" t="n">
         <v>0</v>
@@ -7122,27 +7122,27 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr">
@@ -7162,29 +7162,29 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>8.75</v>
+        <v>1</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>690</v>
-      </c>
-      <c r="O90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7194,12 +7194,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -7234,23 +7234,23 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>1</v>
+        <v>2.42</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
@@ -7317,18 +7317,18 @@
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="15" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="O92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7389,16 +7389,16 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>187.5</v>
+        <v>787.5</v>
       </c>
       <c r="O93" s="16" t="n">
         <v>0</v>
@@ -7410,28 +7410,26 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="inlineStr">
-        <is>
-          <t>Paramétrages complémentaires + Vision</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v/>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -7450,29 +7448,29 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>2.42</v>
+        <v>0.5</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="O94" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -10016,12 +10014,12 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
@@ -10031,7 +10029,7 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10047,32 +10045,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H132" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H132" s="14" t="inlineStr"/>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L132" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M132" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L132" s="14" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
       <c r="N132" s="15" t="n">
         <v>0</v>
       </c>
@@ -10086,12 +10072,12 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -10101,7 +10087,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10124,17 +10110,25 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L133" s="11" t="inlineStr"/>
-      <c r="M133" s="11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N133" s="12" t="n">
         <v>0</v>
       </c>
@@ -10148,28 +10142,26 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E134" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E134" s="14" t="n">
+        <v/>
       </c>
       <c r="F134" s="14" t="inlineStr">
         <is>
@@ -10183,7 +10175,7 @@
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
@@ -10195,7 +10187,7 @@
         <v>35</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L134" s="14" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -10212,23 +10204,27 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C135" s="11" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr">
@@ -10243,19 +10239,19 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>8</v>
+        <v>1.25</v>
       </c>
       <c r="L135" s="11" t="inlineStr"/>
       <c r="M135" s="11" t="inlineStr"/>
@@ -10272,27 +10268,23 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C136" s="14" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C136" s="14" t="inlineStr"/>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F136" s="14" t="inlineStr">
@@ -10307,19 +10299,19 @@
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="L136" s="14" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -10336,21 +10328,29 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C137" s="11" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E137" s="11" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10358,17 +10358,21 @@
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H137" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K137" s="11" t="n">
         <v>0.5</v>
@@ -10388,18 +10392,18 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr"/>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E138" s="14" t="inlineStr"/>
@@ -10416,14 +10420,14 @@
       <c r="H138" s="14" t="inlineStr"/>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10438,31 +10442,187 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="17" t="inlineStr">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1320</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr"/>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr"/>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr"/>
+      <c r="I139" s="11" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L139" s="11" t="inlineStr"/>
+      <c r="M139" s="11" t="inlineStr"/>
+      <c r="N139" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B140" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C140" s="14" t="inlineStr"/>
+      <c r="D140" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr"/>
+      <c r="F140" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G140" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr"/>
+      <c r="I140" s="14" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="J140" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="K140" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+      <c r="N140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr"/>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr"/>
+      <c r="F141" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr"/>
+      <c r="I141" s="11" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J141" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K141" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr"/>
+      <c r="M141" s="11" t="inlineStr"/>
+      <c r="N141" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B139" s="17" t="inlineStr"/>
-      <c r="C139" s="17" t="inlineStr"/>
-      <c r="D139" s="17" t="inlineStr"/>
-      <c r="E139" s="17" t="inlineStr"/>
-      <c r="F139" s="17" t="inlineStr"/>
-      <c r="G139" s="17" t="inlineStr"/>
-      <c r="H139" s="17" t="inlineStr"/>
-      <c r="I139" s="17" t="inlineStr"/>
-      <c r="J139" s="17" t="inlineStr"/>
-      <c r="K139" s="17" t="inlineStr"/>
-      <c r="L139" s="17" t="inlineStr"/>
-      <c r="M139" s="17" t="inlineStr"/>
-      <c r="N139" s="18" t="n">
-        <v>66961.194</v>
-      </c>
-      <c r="O139" s="18" t="n">
+      <c r="B142" s="17" t="inlineStr"/>
+      <c r="C142" s="17" t="inlineStr"/>
+      <c r="D142" s="17" t="inlineStr"/>
+      <c r="E142" s="17" t="inlineStr"/>
+      <c r="F142" s="17" t="inlineStr"/>
+      <c r="G142" s="17" t="inlineStr"/>
+      <c r="H142" s="17" t="inlineStr"/>
+      <c r="I142" s="17" t="inlineStr"/>
+      <c r="J142" s="17" t="inlineStr"/>
+      <c r="K142" s="17" t="inlineStr"/>
+      <c r="L142" s="17" t="inlineStr"/>
+      <c r="M142" s="17" t="inlineStr"/>
+      <c r="N142" s="18" t="n">
+        <v>66066.194</v>
+      </c>
+      <c r="O142" s="18" t="n">
         <v>16406.71</v>
       </c>
-      <c r="P139" s="18" t="n">
-        <v>81.53</v>
+      <c r="P142" s="18" t="n">
+        <v>79.83</v>
       </c>
     </row>
   </sheetData>
@@ -10602,6 +10762,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11251,16 +11414,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>148.5</v>
+        <v>151.75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>185.5</v>
+        <v>189.75</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>66.25</v>
@@ -11270,7 +11433,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11475,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>101</v>
+        <v>105.5</v>
       </c>
     </row>
   </sheetData>
@@ -11476,7 +11639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11500,7 +11663,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 14 commande(s)</t>
+          <t>Épics créées ce mois — 15 commande(s)</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11718,12 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35212</t>
+          <t>PDMDEP-35236</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35206</t>
+          <t>PDMDEP-35227</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -11570,7 +11733,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+          <t>VILLE DE CHAUNY</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -11580,7 +11743,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -11590,7 +11753,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00179038</t>
+          <t>00179114</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
@@ -11600,22 +11763,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35171</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35165</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LORGUES</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -11635,22 +11798,22 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00178865</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35156</t>
+          <t>PDMDEP-35171</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35148</t>
+          <t>PDMDEP-35165</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -11660,7 +11823,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Les Portes En Ré</t>
+          <t>MAIRIE DE LORGUES</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -11680,32 +11843,32 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00178841</t>
+          <t>00178865</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35139</t>
+          <t>PDMDEP-35156</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35148</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>Mairie de Les Portes En Ré</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -11715,7 +11878,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -11725,22 +11888,22 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00178821</t>
+          <t>00178841</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>2035</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -11750,7 +11913,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -11770,22 +11933,22 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>985</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35088</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35082</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -11795,7 +11958,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>FREJUS</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -11815,32 +11978,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00152501</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>3541.5</v>
+        <v>985</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35008</t>
+          <t>PDMDEP-35088</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35000</t>
+          <t>PDMDEP-35082</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
+          <t>FREJUS</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -11850,7 +12013,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -11860,32 +12023,32 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00178436</t>
+          <t>00152501</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>500</v>
+        <v>3541.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-35008</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -11905,37 +12068,37 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178436</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>4050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35188</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35184</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -11950,32 +12113,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00178947</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1736</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35041</t>
+          <t>PDMDEP-35188</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -11995,32 +12158,32 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00178778</t>
+          <t>00178947</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34993</t>
+          <t>PDMDEP-35041</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34989</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -12040,32 +12203,32 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00178306</t>
+          <t>00178778</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -12085,22 +12248,22 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34970</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34966</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -12110,7 +12273,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -12130,83 +12293,107 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>00146508</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-34970</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34966</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Commune de Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>00146508</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I18" s="26" t="n">
+      <c r="I19" s="25" t="n">
         <v>2300</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>14 commande(s)</t>
-        </is>
-      </c>
-      <c r="I19" s="24" t="n">
-        <v>19898</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B20" s="17" t="n"/>
@@ -12217,17 +12404,17 @@
       <c r="G20" s="17" t="n"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>6 commande(s)</t>
+          <t>15 commande(s)</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>7736</v>
+        <v>19898</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B21" s="17" t="n"/>
@@ -12238,10 +12425,31 @@
       <c r="G21" s="17" t="n"/>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>8 commande(s)</t>
+          <t>6 commande(s)</t>
         </is>
       </c>
       <c r="I21" s="24" t="n">
+        <v>7736</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>9 commande(s)</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="n">
         <v>12162</v>
       </c>
     </row>
